--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="74">
   <si>
     <t xml:space="preserve">NCM</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">095</t>
   </si>
   <si>
-    <t xml:space="preserve">00,80</t>
+    <t xml:space="preserve">0,80</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE CÁLCIO (CAL APAGADA)</t>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">092</t>
   </si>
   <si>
-    <t xml:space="preserve">02,21</t>
+    <t xml:space="preserve">2,21</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO CLORÍDRICO (SOLUÇÃO AQUOSA)</t>
@@ -61,19 +61,19 @@
     <t xml:space="preserve">033</t>
   </si>
   <si>
-    <t xml:space="preserve">01,15</t>
+    <t xml:space="preserve">1,15</t>
   </si>
   <si>
     <t xml:space="preserve">028</t>
   </si>
   <si>
-    <t xml:space="preserve">01,19</t>
+    <t xml:space="preserve">1,19</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO SULFÚRICO</t>
   </si>
   <si>
-    <t xml:space="preserve">01,84</t>
+    <t xml:space="preserve">1,84</t>
   </si>
   <si>
     <t xml:space="preserve">098</t>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t xml:space="preserve">CARBONATO DE CÁLCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,80</t>
   </si>
   <si>
     <t xml:space="preserve">DICROMATO DE SÓDIO</t>
@@ -554,7 +551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.55"/>
@@ -966,7 +963,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>20926963000128</v>
@@ -977,13 +974,13 @@
         <v>28413000</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>20926963000128</v>
@@ -994,7 +991,7 @@
         <v>28415014</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>22</v>
@@ -1011,13 +1008,13 @@
         <v>28416100</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>20926963000128</v>
@@ -1028,10 +1025,10 @@
         <v>28470000</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>1.29</v>
@@ -1045,13 +1042,13 @@
         <v>29023000</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>20926963000128</v>
@@ -1062,7 +1059,7 @@
         <v>29024200</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>22</v>
@@ -1079,13 +1076,13 @@
         <v>29031200</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>20926963000128</v>
@@ -1096,7 +1093,7 @@
         <v>29032300</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>6</v>
@@ -1113,13 +1110,13 @@
         <v>29051100</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>20926963000128</v>
@@ -1130,13 +1127,13 @@
         <v>29051220</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>20926963000128</v>
@@ -1147,7 +1144,7 @@
         <v>29051300</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>22</v>
@@ -1164,13 +1161,13 @@
         <v>29051410</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>20926963000128</v>
@@ -1181,13 +1178,13 @@
         <v>29141100</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>20926963000128</v>
@@ -1198,13 +1195,13 @@
         <v>29141200</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>20926963000128</v>
@@ -1215,7 +1212,7 @@
         <v>29151100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
@@ -1232,7 +1229,7 @@
         <v>29152100</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>22</v>
@@ -1249,13 +1246,13 @@
         <v>29153100</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>20926963000128</v>
@@ -1266,7 +1263,7 @@
         <v>29153300</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>22</v>
@@ -1283,7 +1280,7 @@
         <v>29153939</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>18</v>
@@ -1300,10 +1297,10 @@
         <v>31021010</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>1.32</v>
@@ -1317,16 +1314,764 @@
         <v>38021000</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>20926963000128</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="n">
+        <v>22071010</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="n">
+        <v>25222000</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="n">
+        <v>28092011</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="n">
+        <v>28100010</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="n">
+        <v>28141000</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="n">
+        <v>28142000</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="n">
+        <v>28151100</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="n">
+        <v>28151200</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="n">
+        <v>28152000</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="n">
+        <v>28251020</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="n">
+        <v>28271000</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="n">
+        <v>28272090</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="n">
+        <v>28289011</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="n">
+        <v>28321090</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="n">
+        <v>28331110</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="n">
+        <v>28362010</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="n">
+        <v>28363000</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="n">
+        <v>28364000</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="n">
+        <v>28365000</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="n">
+        <v>28413000</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="n">
+        <v>28415014</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="n">
+        <v>28416100</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="n">
+        <v>29023000</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="n">
+        <v>29024200</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="n">
+        <v>29031200</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="n">
+        <v>29032300</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E45" s="6" t="n">
-        <v>20926963000128</v>
+      <c r="C76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="n">
+        <v>29051100</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="n">
+        <v>29051220</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="n">
+        <v>29051300</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="n">
+        <v>29051410</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="n">
+        <v>29141100</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="n">
+        <v>29141200</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="n">
+        <v>29151100</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="n">
+        <v>29152100</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="n">
+        <v>29153100</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="n">
+        <v>29153300</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="n">
+        <v>29153939</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="n">
+        <v>31021010</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="n">
+        <v>38021000</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>61133096000312</v>
       </c>
     </row>
   </sheetData>

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -626,7 +626,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>20926963000127</v>
+        <v>20926963000128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -643,7 +643,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>20926963000128</v>
+        <v>20926963000127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1374,7 +1374,7 @@
         <v>13</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>61133096000312</v>
+        <v>61133096000311</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1408,7 +1408,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>61133096000312</v>
+        <v>61133096000311</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
   <si>
     <t xml:space="preserve">NCM</t>
   </si>
@@ -551,7 +551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.55"/>
@@ -2072,6 +2072,754 @@
       </c>
       <c r="E89" s="1" t="n">
         <v>61133096000312</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="n">
+        <v>22071010</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="n">
+        <v>25222000</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="n">
+        <v>28092011</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="n">
+        <v>28100010</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="n">
+        <v>28141000</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3" t="n">
+        <v>28142000</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="n">
+        <v>28151100</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="n">
+        <v>28151200</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="n">
+        <v>28152000</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="3" t="n">
+        <v>28251020</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="3" t="n">
+        <v>28271000</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="n">
+        <v>28272090</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="3" t="n">
+        <v>28289011</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="3" t="n">
+        <v>28321090</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="n">
+        <v>28331110</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="3" t="n">
+        <v>28362010</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="3" t="n">
+        <v>28363000</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="n">
+        <v>28364000</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="n">
+        <v>28365000</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3" t="n">
+        <v>28413000</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="n">
+        <v>28415014</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="n">
+        <v>28416100</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="n">
+        <v>29023000</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E117" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3" t="n">
+        <v>29024200</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="3" t="n">
+        <v>29031200</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E119" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="3" t="n">
+        <v>29032300</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="3" t="n">
+        <v>29051100</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="3" t="n">
+        <v>29051220</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="3" t="n">
+        <v>29051300</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E123" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="3" t="n">
+        <v>29051410</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="n">
+        <v>29141100</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="3" t="n">
+        <v>29141200</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="n">
+        <v>29151100</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E127" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="3" t="n">
+        <v>29152100</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="3" t="n">
+        <v>29153100</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="3" t="n">
+        <v>29153300</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="3" t="n">
+        <v>29153939</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E131" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="3" t="n">
+        <v>31021010</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="3" t="n">
+        <v>38021000</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>33931486001455</v>
       </c>
     </row>
   </sheetData>

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="74">
   <si>
     <t xml:space="preserve">NCM</t>
   </si>
@@ -551,7 +551,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.55"/>
@@ -2820,6 +2820,754 @@
       </c>
       <c r="E133" s="6" t="n">
         <v>33931486001455</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="3" t="n">
+        <v>22071010</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="3" t="n">
+        <v>25222000</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="3" t="n">
+        <v>28092011</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="3" t="n">
+        <v>28100010</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="3" t="n">
+        <v>28141000</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="3" t="n">
+        <v>28142000</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E143" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="3" t="n">
+        <v>28151100</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E144" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="3" t="n">
+        <v>28151200</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="3" t="n">
+        <v>28152000</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E146" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="3" t="n">
+        <v>28251020</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E147" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="3" t="n">
+        <v>28271000</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E148" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="3" t="n">
+        <v>28272090</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="3" t="n">
+        <v>28289011</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E150" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="3" t="n">
+        <v>28321090</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="3" t="n">
+        <v>28331110</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E152" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="3" t="n">
+        <v>28362010</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E153" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="3" t="n">
+        <v>28363000</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E154" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="3" t="n">
+        <v>28364000</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E155" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="3" t="n">
+        <v>28365000</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E156" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="3" t="n">
+        <v>28413000</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="3" t="n">
+        <v>28415014</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A159" s="3" t="n">
+        <v>28416100</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D160" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A161" s="3" t="n">
+        <v>29023000</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A162" s="3" t="n">
+        <v>29024200</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D162" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="3" t="n">
+        <v>29031200</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="3" t="n">
+        <v>29032300</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E164" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A165" s="3" t="n">
+        <v>29051100</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A166" s="3" t="n">
+        <v>29051220</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E166" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3" t="n">
+        <v>29051300</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A168" s="3" t="n">
+        <v>29051410</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="3" t="n">
+        <v>29141100</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A170" s="3" t="n">
+        <v>29141200</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A171" s="3" t="n">
+        <v>29151100</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E171" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="3" t="n">
+        <v>29152100</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A173" s="3" t="n">
+        <v>29153100</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E173" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A174" s="3" t="n">
+        <v>29153300</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E174" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A175" s="3" t="n">
+        <v>29153939</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E175" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A176" s="3" t="n">
+        <v>31021010</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E176" s="1" t="n">
+        <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A177" s="3" t="n">
+        <v>38021000</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E177" s="1" t="n">
+        <v>72441454000532</v>
       </c>
     </row>
   </sheetData>

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="75">
   <si>
     <t xml:space="preserve">NCM</t>
   </si>
@@ -43,7 +43,7 @@
     <t xml:space="preserve">095</t>
   </si>
   <si>
-    <t xml:space="preserve">0,80</t>
+    <t xml:space="preserve">0.80</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE CÁLCIO (CAL APAGADA)</t>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">092</t>
   </si>
   <si>
-    <t xml:space="preserve">2,21</t>
+    <t xml:space="preserve">2.21</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO CLORÍDRICO (SOLUÇÃO AQUOSA)</t>
@@ -61,19 +61,19 @@
     <t xml:space="preserve">033</t>
   </si>
   <si>
-    <t xml:space="preserve">1,15</t>
+    <t xml:space="preserve">1.15</t>
   </si>
   <si>
     <t xml:space="preserve">028</t>
   </si>
   <si>
-    <t xml:space="preserve">1,19</t>
+    <t xml:space="preserve">1.19</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO SULFÚRICO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,84</t>
+    <t xml:space="preserve">1.84</t>
   </si>
   <si>
     <t xml:space="preserve">098</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">AMÔNIA (GÁS - AMONÍACO ANIDRO)</t>
   </si>
   <si>
-    <t xml:space="preserve">0,60</t>
+    <t xml:space="preserve">0.60</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE AMÔNIO (AMONÍACO EM SOLUÇÃO AQUOSA)</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (SÓLIDO)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,10</t>
+    <t xml:space="preserve">2.10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (EM SOLUÇÃO AQUOSA)</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">050</t>
   </si>
   <si>
-    <t xml:space="preserve">1,10</t>
+    <t xml:space="preserve">1.10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE POTÁSSIO</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">BICARBONATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2,20</t>
+    <t xml:space="preserve">2.20</t>
   </si>
   <si>
     <t xml:space="preserve">CARBONATO DE POTÁSSIO</t>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">DICROMATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,20</t>
+    <t xml:space="preserve">1.20</t>
   </si>
   <si>
     <t xml:space="preserve">DICROMATO DE POTÁSSIO</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">PERMANGANATO DE POTÁSSIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2,70</t>
+    <t xml:space="preserve">2.70</t>
   </si>
   <si>
     <t xml:space="preserve">PERÓXIDO DE HIDROGÊNIO</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">TOLUENO (OUTROS)</t>
   </si>
   <si>
-    <t xml:space="preserve">0,90</t>
+    <t xml:space="preserve">0.90</t>
   </si>
   <si>
     <t xml:space="preserve">XILENOS (M-XILENO)</t>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">CLORETO DE METILENO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,30</t>
+    <t xml:space="preserve">1.30</t>
   </si>
   <si>
     <t xml:space="preserve">TETRACLOROETILENO</t>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t xml:space="preserve">CARVÃO ATIVADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00220359000174</t>
   </si>
 </sst>
 </file>
@@ -358,7 +361,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -551,14 +554,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="19.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1339,7 +1342,7 @@
       <c r="D46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1356,7 +1359,7 @@
       <c r="D47" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1373,7 +1376,7 @@
       <c r="D48" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>61133096000311</v>
       </c>
     </row>
@@ -1390,7 +1393,7 @@
       <c r="D49" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1407,7 +1410,7 @@
       <c r="D50" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>61133096000311</v>
       </c>
     </row>
@@ -1424,7 +1427,7 @@
       <c r="D51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1441,7 +1444,7 @@
       <c r="D52" s="5" t="n">
         <v>1.68</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1458,7 +1461,7 @@
       <c r="D53" s="5" t="n">
         <v>1.44</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1475,7 +1478,7 @@
       <c r="D54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1492,7 +1495,7 @@
       <c r="D55" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1509,7 +1512,7 @@
       <c r="D56" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1526,7 +1529,7 @@
       <c r="D57" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1543,7 +1546,7 @@
       <c r="D58" s="5" t="n">
         <v>2.04</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1560,7 +1563,7 @@
       <c r="D59" s="5" t="n">
         <v>1.21</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1577,7 +1580,7 @@
       <c r="D60" s="5" t="n">
         <v>1.53</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1594,7 +1597,7 @@
       <c r="D61" s="5" t="n">
         <v>2.15</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1611,7 +1614,7 @@
       <c r="D62" s="5" t="n">
         <v>1.84</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1628,7 +1631,7 @@
       <c r="D63" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1645,7 +1648,7 @@
       <c r="D64" s="5" t="n">
         <v>1.37</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1662,7 +1665,7 @@
       <c r="D65" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1679,7 +1682,7 @@
       <c r="D66" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1696,7 +1699,7 @@
       <c r="D67" s="5" t="n">
         <v>2.43</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1713,7 +1716,7 @@
       <c r="D68" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1730,7 +1733,7 @@
       <c r="D69" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1747,7 +1750,7 @@
       <c r="D70" s="5" t="n">
         <v>2.67</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1764,7 +1767,7 @@
       <c r="D71" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1781,7 +1784,7 @@
       <c r="D72" s="5" t="n">
         <v>1.29</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1798,7 +1801,7 @@
       <c r="D73" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1815,7 +1818,7 @@
       <c r="D74" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1832,7 +1835,7 @@
       <c r="D75" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1849,7 +1852,7 @@
       <c r="D76" s="5" t="n">
         <v>1.63</v>
       </c>
-      <c r="E76" s="1" t="n">
+      <c r="E76" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1866,7 +1869,7 @@
       <c r="D77" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="E77" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1883,7 +1886,7 @@
       <c r="D78" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="1" t="n">
+      <c r="E78" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1900,7 +1903,7 @@
       <c r="D79" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="E79" s="1" t="n">
+      <c r="E79" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1917,7 +1920,7 @@
       <c r="D80" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="1" t="n">
+      <c r="E80" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1934,7 +1937,7 @@
       <c r="D81" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E81" s="1" t="n">
+      <c r="E81" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1951,7 +1954,7 @@
       <c r="D82" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="1" t="n">
+      <c r="E82" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1968,7 +1971,7 @@
       <c r="D83" s="5" t="n">
         <v>1.22</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="E83" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -1985,7 +1988,7 @@
       <c r="D84" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E84" s="1" t="n">
+      <c r="E84" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2002,7 +2005,7 @@
       <c r="D85" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E85" s="1" t="n">
+      <c r="E85" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2019,7 +2022,7 @@
       <c r="D86" s="5" t="n">
         <v>0.88</v>
       </c>
-      <c r="E86" s="1" t="n">
+      <c r="E86" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2036,7 +2039,7 @@
       <c r="D87" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="E87" s="1" t="n">
+      <c r="E87" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2053,7 +2056,7 @@
       <c r="D88" s="5" t="n">
         <v>1.32</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E88" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2070,7 +2073,7 @@
       <c r="D89" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E89" s="1" t="n">
+      <c r="E89" s="2" t="n">
         <v>61133096000312</v>
       </c>
     </row>
@@ -2835,7 +2838,7 @@
       <c r="D134" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="E134" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2852,7 +2855,7 @@
       <c r="D135" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E135" s="1" t="n">
+      <c r="E135" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2869,7 +2872,7 @@
       <c r="D136" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="E136" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2886,7 +2889,7 @@
       <c r="D137" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="E137" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2903,7 +2906,7 @@
       <c r="D138" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E138" s="1" t="n">
+      <c r="E138" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2920,7 +2923,7 @@
       <c r="D139" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E139" s="1" t="n">
+      <c r="E139" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2937,7 +2940,7 @@
       <c r="D140" s="5" t="n">
         <v>1.68</v>
       </c>
-      <c r="E140" s="1" t="n">
+      <c r="E140" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2954,7 +2957,7 @@
       <c r="D141" s="5" t="n">
         <v>1.44</v>
       </c>
-      <c r="E141" s="1" t="n">
+      <c r="E141" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2971,7 +2974,7 @@
       <c r="D142" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E142" s="1" t="n">
+      <c r="E142" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -2988,7 +2991,7 @@
       <c r="D143" s="5" t="n">
         <v>0.91</v>
       </c>
-      <c r="E143" s="1" t="n">
+      <c r="E143" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3005,7 +3008,7 @@
       <c r="D144" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E144" s="1" t="n">
+      <c r="E144" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3022,7 +3025,7 @@
       <c r="D145" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="1" t="n">
+      <c r="E145" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3039,7 +3042,7 @@
       <c r="D146" s="5" t="n">
         <v>2.04</v>
       </c>
-      <c r="E146" s="1" t="n">
+      <c r="E146" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3056,7 +3059,7 @@
       <c r="D147" s="5" t="n">
         <v>1.21</v>
       </c>
-      <c r="E147" s="1" t="n">
+      <c r="E147" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3073,7 +3076,7 @@
       <c r="D148" s="5" t="n">
         <v>1.53</v>
       </c>
-      <c r="E148" s="1" t="n">
+      <c r="E148" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3090,7 +3093,7 @@
       <c r="D149" s="5" t="n">
         <v>2.15</v>
       </c>
-      <c r="E149" s="1" t="n">
+      <c r="E149" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3107,7 +3110,7 @@
       <c r="D150" s="5" t="n">
         <v>1.84</v>
       </c>
-      <c r="E150" s="1" t="n">
+      <c r="E150" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3124,7 +3127,7 @@
       <c r="D151" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E151" s="1" t="n">
+      <c r="E151" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3141,7 +3144,7 @@
       <c r="D152" s="5" t="n">
         <v>1.37</v>
       </c>
-      <c r="E152" s="1" t="n">
+      <c r="E152" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3158,7 +3161,7 @@
       <c r="D153" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E153" s="1" t="n">
+      <c r="E153" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3175,7 +3178,7 @@
       <c r="D154" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E154" s="1" t="n">
+      <c r="E154" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3192,7 +3195,7 @@
       <c r="D155" s="5" t="n">
         <v>2.43</v>
       </c>
-      <c r="E155" s="1" t="n">
+      <c r="E155" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3209,7 +3212,7 @@
       <c r="D156" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E156" s="1" t="n">
+      <c r="E156" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3226,7 +3229,7 @@
       <c r="D157" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E157" s="1" t="n">
+      <c r="E157" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3243,7 +3246,7 @@
       <c r="D158" s="5" t="n">
         <v>2.67</v>
       </c>
-      <c r="E158" s="1" t="n">
+      <c r="E158" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3260,7 +3263,7 @@
       <c r="D159" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E159" s="1" t="n">
+      <c r="E159" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3277,7 +3280,7 @@
       <c r="D160" s="5" t="n">
         <v>1.29</v>
       </c>
-      <c r="E160" s="1" t="n">
+      <c r="E160" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3294,7 +3297,7 @@
       <c r="D161" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E161" s="1" t="n">
+      <c r="E161" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3311,7 +3314,7 @@
       <c r="D162" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="E162" s="1" t="n">
+      <c r="E162" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3328,7 +3331,7 @@
       <c r="D163" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E163" s="1" t="n">
+      <c r="E163" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3345,7 +3348,7 @@
       <c r="D164" s="5" t="n">
         <v>1.63</v>
       </c>
-      <c r="E164" s="1" t="n">
+      <c r="E164" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3362,7 +3365,7 @@
       <c r="D165" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E165" s="1" t="n">
+      <c r="E165" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3379,7 +3382,7 @@
       <c r="D166" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E166" s="1" t="n">
+      <c r="E166" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3396,7 +3399,7 @@
       <c r="D167" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="E167" s="1" t="n">
+      <c r="E167" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3413,7 +3416,7 @@
       <c r="D168" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="1" t="n">
+      <c r="E168" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3430,7 +3433,7 @@
       <c r="D169" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E169" s="1" t="n">
+      <c r="E169" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3447,7 +3450,7 @@
       <c r="D170" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E170" s="1" t="n">
+      <c r="E170" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3464,7 +3467,7 @@
       <c r="D171" s="5" t="n">
         <v>1.22</v>
       </c>
-      <c r="E171" s="1" t="n">
+      <c r="E171" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3481,7 +3484,7 @@
       <c r="D172" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E172" s="1" t="n">
+      <c r="E172" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3498,7 +3501,7 @@
       <c r="D173" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E173" s="1" t="n">
+      <c r="E173" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3515,7 +3518,7 @@
       <c r="D174" s="5" t="n">
         <v>0.88</v>
       </c>
-      <c r="E174" s="1" t="n">
+      <c r="E174" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3532,7 +3535,7 @@
       <c r="D175" s="5" t="n">
         <v>0.87</v>
       </c>
-      <c r="E175" s="1" t="n">
+      <c r="E175" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3549,7 +3552,7 @@
       <c r="D176" s="5" t="n">
         <v>1.32</v>
       </c>
-      <c r="E176" s="1" t="n">
+      <c r="E176" s="2" t="n">
         <v>72441454000532</v>
       </c>
     </row>
@@ -3566,8 +3569,756 @@
       <c r="D177" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E177" s="1" t="n">
+      <c r="E177" s="2" t="n">
         <v>72441454000532</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A178" s="3" t="n">
+        <v>22071010</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="3" t="n">
+        <v>25222000</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A180" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A181" s="3" t="n">
+        <v>28061020</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A182" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A183" s="3" t="n">
+        <v>28070010</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A184" s="3" t="n">
+        <v>28092011</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A185" s="3" t="n">
+        <v>28100010</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A186" s="3" t="n">
+        <v>28141000</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A187" s="3" t="n">
+        <v>28142000</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A188" s="3" t="n">
+        <v>28151100</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A189" s="3" t="n">
+        <v>28151200</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A190" s="3" t="n">
+        <v>28152000</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A191" s="3" t="n">
+        <v>28251020</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A192" s="3" t="n">
+        <v>28271000</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D192" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A193" s="3" t="n">
+        <v>28272090</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D193" s="5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A194" s="3" t="n">
+        <v>28289011</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D194" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A195" s="3" t="n">
+        <v>28321090</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="3" t="n">
+        <v>28331110</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D196" s="5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A197" s="3" t="n">
+        <v>28362010</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A198" s="3" t="n">
+        <v>28363000</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="3" t="n">
+        <v>28364000</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D199" s="5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A200" s="3" t="n">
+        <v>28365000</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A201" s="3" t="n">
+        <v>28413000</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A202" s="3" t="n">
+        <v>28415014</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D202" s="5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A203" s="3" t="n">
+        <v>28416100</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A204" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D204" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A205" s="3" t="n">
+        <v>29023000</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="3" t="n">
+        <v>29024200</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D206" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A207" s="3" t="n">
+        <v>29031200</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A208" s="3" t="n">
+        <v>29032300</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A209" s="3" t="n">
+        <v>29051100</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A210" s="3" t="n">
+        <v>29051220</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A211" s="3" t="n">
+        <v>29051300</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D211" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A212" s="3" t="n">
+        <v>29051410</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A213" s="3" t="n">
+        <v>29141100</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A214" s="3" t="n">
+        <v>29141200</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A215" s="3" t="n">
+        <v>29151100</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D215" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A216" s="3" t="n">
+        <v>29152100</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A217" s="3" t="n">
+        <v>29153100</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A218" s="3" t="n">
+        <v>29153300</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D218" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A219" s="3" t="n">
+        <v>29153939</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D219" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A220" s="3" t="n">
+        <v>31021010</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D220" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A221" s="3" t="n">
+        <v>38021000</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.80</t>
+    <t xml:space="preserve">0,80</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE CÁLCIO (CAL APAGADA)</t>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21</t>
+    <t xml:space="preserve">2,21</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO CLORÍDRICO (SOLUÇÃO AQUOSA)</t>
@@ -61,19 +61,19 @@
     <t xml:space="preserve">033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15</t>
+    <t xml:space="preserve">1,15</t>
   </si>
   <si>
     <t xml:space="preserve">028</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19</t>
+    <t xml:space="preserve">1,19</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO SULFÚRICO</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84</t>
+    <t xml:space="preserve">1,84</t>
   </si>
   <si>
     <t xml:space="preserve">098</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">AMÔNIA (GÁS - AMONÍACO ANIDRO)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60</t>
+    <t xml:space="preserve">0,60</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE AMÔNIO (AMONÍACO EM SOLUÇÃO AQUOSA)</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (SÓLIDO)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10</t>
+    <t xml:space="preserve">2,10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (EM SOLUÇÃO AQUOSA)</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">050</t>
   </si>
   <si>
-    <t xml:space="preserve">1.10</t>
+    <t xml:space="preserve">1,10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE POTÁSSIO</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">BICARBONATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20</t>
+    <t xml:space="preserve">2,20</t>
   </si>
   <si>
     <t xml:space="preserve">CARBONATO DE POTÁSSIO</t>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">DICROMATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20</t>
+    <t xml:space="preserve">1,20</t>
   </si>
   <si>
     <t xml:space="preserve">DICROMATO DE POTÁSSIO</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">PERMANGANATO DE POTÁSSIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70</t>
+    <t xml:space="preserve">2,70</t>
   </si>
   <si>
     <t xml:space="preserve">PERÓXIDO DE HIDROGÊNIO</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">TOLUENO (OUTROS)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.90</t>
+    <t xml:space="preserve">0,90</t>
   </si>
   <si>
     <t xml:space="preserve">XILENOS (M-XILENO)</t>
@@ -196,7 +196,7 @@
     <t xml:space="preserve">CLORETO DE METILENO</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30</t>
+    <t xml:space="preserve">1,30</t>
   </si>
   <si>
     <t xml:space="preserve">TETRACLOROETILENO</t>

--- a/app/media/densidade_concentracao.xlsx
+++ b/app/media/densidade_concentracao.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="90">
   <si>
     <t xml:space="preserve">NCM</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">095</t>
   </si>
   <si>
-    <t xml:space="preserve">0,80</t>
+    <t xml:space="preserve">00,80</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE CÁLCIO (CAL APAGADA)</t>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">092</t>
   </si>
   <si>
-    <t xml:space="preserve">2,21</t>
+    <t xml:space="preserve">02,21</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO CLORÍDRICO (SOLUÇÃO AQUOSA)</t>
@@ -58,19 +58,19 @@
     <t xml:space="preserve">033</t>
   </si>
   <si>
-    <t xml:space="preserve">1,15</t>
+    <t xml:space="preserve">01,15</t>
   </si>
   <si>
     <t xml:space="preserve">028</t>
   </si>
   <si>
-    <t xml:space="preserve">1,19</t>
+    <t xml:space="preserve">01,19</t>
   </si>
   <si>
     <t xml:space="preserve">ÁCIDO SULFÚRICO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,84</t>
+    <t xml:space="preserve">01,84</t>
   </si>
   <si>
     <t xml:space="preserve">098</t>
@@ -82,16 +82,22 @@
     <t xml:space="preserve">085</t>
   </si>
   <si>
+    <t xml:space="preserve">01,68</t>
+  </si>
+  <si>
     <t xml:space="preserve">ÁCIDO BÓRICO E SEUS SAIS</t>
   </si>
   <si>
     <t xml:space="preserve">099</t>
   </si>
   <si>
+    <t xml:space="preserve">01,44</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMÔNIA (GÁS - AMONÍACO ANIDRO)</t>
   </si>
   <si>
-    <t xml:space="preserve">0,60</t>
+    <t xml:space="preserve">00,60</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE AMÔNIO (AMONÍACO EM SOLUÇÃO AQUOSA)</t>
@@ -100,10 +106,13 @@
     <t xml:space="preserve">024</t>
   </si>
   <si>
+    <t xml:space="preserve">00,91</t>
+  </si>
+  <si>
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (SÓLIDO)</t>
   </si>
   <si>
-    <t xml:space="preserve">2,10</t>
+    <t xml:space="preserve">02,10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE SÓDIO (EM SOLUÇÃO AQUOSA)</t>
@@ -112,7 +121,7 @@
     <t xml:space="preserve">050</t>
   </si>
   <si>
-    <t xml:space="preserve">1,10</t>
+    <t xml:space="preserve">01,10</t>
   </si>
   <si>
     <t xml:space="preserve">HIDRÓXIDO DE POTÁSSIO</t>
@@ -121,21 +130,33 @@
     <t xml:space="preserve">088</t>
   </si>
   <si>
+    <t xml:space="preserve">02,04</t>
+  </si>
+  <si>
     <t xml:space="preserve">HIDROXILAMINA E SEUS SAIS</t>
   </si>
   <si>
     <t xml:space="preserve">096</t>
   </si>
   <si>
+    <t xml:space="preserve">01,21</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLORETO DE AMÔNIO</t>
   </si>
   <si>
+    <t xml:space="preserve">01,53</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLORETO DE CÁLCIO (OUTROS)</t>
   </si>
   <si>
     <t xml:space="preserve">074</t>
   </si>
   <si>
+    <t xml:space="preserve">02,15</t>
+  </si>
+  <si>
     <t xml:space="preserve">HIPOCLORITO DE SÓDIO</t>
   </si>
   <si>
@@ -145,34 +166,43 @@
     <t xml:space="preserve">SULFATO DE SÓDIO ANIDRO</t>
   </si>
   <si>
+    <t xml:space="preserve">01,37</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARBONATO DE SÓDIO ANIDRO</t>
   </si>
   <si>
     <t xml:space="preserve">BICARBONATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2,20</t>
+    <t xml:space="preserve">02,20</t>
   </si>
   <si>
     <t xml:space="preserve">CARBONATO DE POTÁSSIO</t>
   </si>
   <si>
+    <t xml:space="preserve">02,43</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARBONATO DE CÁLCIO</t>
   </si>
   <si>
     <t xml:space="preserve">DICROMATO DE SÓDIO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,20</t>
+    <t xml:space="preserve">01,20</t>
   </si>
   <si>
     <t xml:space="preserve">DICROMATO DE POTÁSSIO</t>
   </si>
   <si>
+    <t xml:space="preserve">02,67</t>
+  </si>
+  <si>
     <t xml:space="preserve">PERMANGANATO DE POTÁSSIO</t>
   </si>
   <si>
-    <t xml:space="preserve">2,70</t>
+    <t xml:space="preserve">02,70</t>
   </si>
   <si>
     <t xml:space="preserve">PERÓXIDO DE HIDROGÊNIO</t>
@@ -181,24 +211,33 @@
     <t xml:space="preserve">090</t>
   </si>
   <si>
+    <t xml:space="preserve">01,29</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOLUENO (OUTROS)</t>
   </si>
   <si>
-    <t xml:space="preserve">0,90</t>
+    <t xml:space="preserve">00,90</t>
   </si>
   <si>
     <t xml:space="preserve">XILENOS (M-XILENO)</t>
   </si>
   <si>
+    <t xml:space="preserve">00,87</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLORETO DE METILENO</t>
   </si>
   <si>
-    <t xml:space="preserve">1,30</t>
+    <t xml:space="preserve">01,30</t>
   </si>
   <si>
     <t xml:space="preserve">TETRACLOROETILENO</t>
   </si>
   <si>
+    <t xml:space="preserve">01,63</t>
+  </si>
+  <si>
     <t xml:space="preserve">ÁLCOOL METÍLICO</t>
   </si>
   <si>
@@ -208,6 +247,9 @@
     <t xml:space="preserve">ÁLCOOL N-BUTÍLICO</t>
   </si>
   <si>
+    <t xml:space="preserve">00,78</t>
+  </si>
+  <si>
     <t xml:space="preserve">ÁLCOOL ISOBUTÍLICO</t>
   </si>
   <si>
@@ -220,6 +262,9 @@
     <t xml:space="preserve">ÁCIDO FÓRMICO</t>
   </si>
   <si>
+    <t xml:space="preserve">01,22</t>
+  </si>
+  <si>
     <t xml:space="preserve">ÁCIDO ACÉTICO</t>
   </si>
   <si>
@@ -229,6 +274,9 @@
     <t xml:space="preserve">ACETATO DE n-BUTILA</t>
   </si>
   <si>
+    <t xml:space="preserve">00,88</t>
+  </si>
+  <si>
     <t xml:space="preserve">ACETATO DE sec-BUTILA</t>
   </si>
   <si>
@@ -236,6 +284,9 @@
   </si>
   <si>
     <t xml:space="preserve">032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01,32</t>
   </si>
   <si>
     <t xml:space="preserve">CARVÃO ATIVADO</t>
@@ -536,7 +587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.55"/>
@@ -654,8 +705,8 @@
       <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>1.68</v>
+      <c r="D8" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -663,13 +714,13 @@
         <v>28100010</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1.44</v>
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -677,13 +728,13 @@
         <v>28141000</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -691,13 +742,13 @@
         <v>28142000</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0.91</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -705,13 +756,13 @@
         <v>28151100</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,13 +770,13 @@
         <v>28151200</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -733,13 +784,13 @@
         <v>28152000</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>2.04</v>
+        <v>35</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -747,13 +798,13 @@
         <v>28251020</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1.21</v>
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -761,13 +812,13 @@
         <v>28271000</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1.53</v>
+        <v>22</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,13 +826,13 @@
         <v>28272090</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>2.15</v>
+        <v>43</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -789,13 +840,13 @@
         <v>28289011</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>1.84</v>
+        <v>22</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -803,13 +854,13 @@
         <v>28321090</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -817,13 +868,13 @@
         <v>28331110</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>1.37</v>
+      <c r="D20" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -831,13 +882,13 @@
         <v>28362010</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -845,13 +896,13 @@
         <v>28363000</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -859,13 +910,13 @@
         <v>28364000</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>2.43</v>
+      <c r="D23" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -873,7 +924,7 @@
         <v>28365000</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>17</v>
@@ -887,13 +938,13 @@
         <v>28413000</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -901,13 +952,13 @@
         <v>28415014</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>2.67</v>
+        <v>22</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -915,13 +966,13 @@
         <v>28416100</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -929,13 +980,13 @@
         <v>28470000</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1.29</v>
+        <v>62</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -943,13 +994,13 @@
         <v>29023000</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,13 +1008,13 @@
         <v>29024200</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>0.87</v>
+        <v>22</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -971,13 +1022,13 @@
         <v>29031200</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -985,13 +1036,13 @@
         <v>29032300</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>1.63</v>
+      <c r="D32" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -999,10 +1050,10 @@
         <v>29051100</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>6</v>
@@ -1013,10 +1064,10 @@
         <v>29051220</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>6</v>
@@ -1027,13 +1078,13 @@
         <v>29051300</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0.78</v>
+        <v>22</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1041,10 +1092,10 @@
         <v>29051410</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>6</v>
@@ -1055,10 +1106,10 @@
         <v>29141100</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>6</v>
@@ -1069,10 +1120,10 @@
         <v>29141200</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>6</v>
@@ -1083,13 +1134,13 @@
         <v>29151100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>1.22</v>
+      <c r="D39" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1097,13 +1148,13 @@
         <v>29152100</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,13 +1162,13 @@
         <v>29153100</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1125,13 +1176,13 @@
         <v>29153300</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>0.88</v>
+        <v>22</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1139,13 +1190,13 @@
         <v>29153939</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>0.87</v>
+      <c r="D43" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1153,13 +1204,13 @@
         <v>31021010</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1.32</v>
+        <v>87</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1167,1070 +1218,14 @@
         <v>38021000</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
-      <c r="B46" s="0"/>
-      <c r="C46" s="0"/>
-      <c r="D46" s="0"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0"/>
-      <c r="B47" s="0"/>
-      <c r="C47" s="0"/>
-      <c r="D47" s="0"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0"/>
-      <c r="B48" s="0"/>
-      <c r="C48" s="0"/>
-      <c r="D48" s="0"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0"/>
-      <c r="B49" s="0"/>
-      <c r="C49" s="0"/>
-      <c r="D49" s="0"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0"/>
-      <c r="B50" s="0"/>
-      <c r="C50" s="0"/>
-      <c r="D50" s="0"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0"/>
-      <c r="B51" s="0"/>
-      <c r="C51" s="0"/>
-      <c r="D51" s="0"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0"/>
-      <c r="B52" s="0"/>
-      <c r="C52" s="0"/>
-      <c r="D52" s="0"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0"/>
-      <c r="B53" s="0"/>
-      <c r="C53" s="0"/>
-      <c r="D53" s="0"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0"/>
-      <c r="B54" s="0"/>
-      <c r="C54" s="0"/>
-      <c r="D54" s="0"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0"/>
-      <c r="B55" s="0"/>
-      <c r="C55" s="0"/>
-      <c r="D55" s="0"/>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0"/>
-      <c r="B56" s="0"/>
-      <c r="C56" s="0"/>
-      <c r="D56" s="0"/>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0"/>
-      <c r="B57" s="0"/>
-      <c r="C57" s="0"/>
-      <c r="D57" s="0"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0"/>
-      <c r="B58" s="0"/>
-      <c r="C58" s="0"/>
-      <c r="D58" s="0"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0"/>
-      <c r="B59" s="0"/>
-      <c r="C59" s="0"/>
-      <c r="D59" s="0"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0"/>
-      <c r="B60" s="0"/>
-      <c r="C60" s="0"/>
-      <c r="D60" s="0"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0"/>
-      <c r="B61" s="0"/>
-      <c r="C61" s="0"/>
-      <c r="D61" s="0"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0"/>
-      <c r="B62" s="0"/>
-      <c r="C62" s="0"/>
-      <c r="D62" s="0"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0"/>
-      <c r="B63" s="0"/>
-      <c r="C63" s="0"/>
-      <c r="D63" s="0"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0"/>
-      <c r="B64" s="0"/>
-      <c r="C64" s="0"/>
-      <c r="D64" s="0"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0"/>
-      <c r="B65" s="0"/>
-      <c r="C65" s="0"/>
-      <c r="D65" s="0"/>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0"/>
-      <c r="B66" s="0"/>
-      <c r="C66" s="0"/>
-      <c r="D66" s="0"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0"/>
-      <c r="B67" s="0"/>
-      <c r="C67" s="0"/>
-      <c r="D67" s="0"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0"/>
-      <c r="B68" s="0"/>
-      <c r="C68" s="0"/>
-      <c r="D68" s="0"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0"/>
-      <c r="B69" s="0"/>
-      <c r="C69" s="0"/>
-      <c r="D69" s="0"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0"/>
-      <c r="B70" s="0"/>
-      <c r="C70" s="0"/>
-      <c r="D70" s="0"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0"/>
-      <c r="B71" s="0"/>
-      <c r="C71" s="0"/>
-      <c r="D71" s="0"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0"/>
-      <c r="B72" s="0"/>
-      <c r="C72" s="0"/>
-      <c r="D72" s="0"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0"/>
-      <c r="B73" s="0"/>
-      <c r="C73" s="0"/>
-      <c r="D73" s="0"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0"/>
-      <c r="B74" s="0"/>
-      <c r="C74" s="0"/>
-      <c r="D74" s="0"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0"/>
-      <c r="B75" s="0"/>
-      <c r="C75" s="0"/>
-      <c r="D75" s="0"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0"/>
-      <c r="B76" s="0"/>
-      <c r="C76" s="0"/>
-      <c r="D76" s="0"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0"/>
-      <c r="B77" s="0"/>
-      <c r="C77" s="0"/>
-      <c r="D77" s="0"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0"/>
-      <c r="B78" s="0"/>
-      <c r="C78" s="0"/>
-      <c r="D78" s="0"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0"/>
-      <c r="B79" s="0"/>
-      <c r="C79" s="0"/>
-      <c r="D79" s="0"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0"/>
-      <c r="B80" s="0"/>
-      <c r="C80" s="0"/>
-      <c r="D80" s="0"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0"/>
-      <c r="B81" s="0"/>
-      <c r="C81" s="0"/>
-      <c r="D81" s="0"/>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0"/>
-      <c r="B82" s="0"/>
-      <c r="C82" s="0"/>
-      <c r="D82" s="0"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0"/>
-      <c r="B83" s="0"/>
-      <c r="C83" s="0"/>
-      <c r="D83" s="0"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0"/>
-      <c r="B84" s="0"/>
-      <c r="C84" s="0"/>
-      <c r="D84" s="0"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0"/>
-      <c r="B85" s="0"/>
-      <c r="C85" s="0"/>
-      <c r="D85" s="0"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0"/>
-      <c r="B86" s="0"/>
-      <c r="C86" s="0"/>
-      <c r="D86" s="0"/>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0"/>
-      <c r="B87" s="0"/>
-      <c r="C87" s="0"/>
-      <c r="D87" s="0"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0"/>
-      <c r="B88" s="0"/>
-      <c r="C88" s="0"/>
-      <c r="D88" s="0"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0"/>
-      <c r="B89" s="0"/>
-      <c r="C89" s="0"/>
-      <c r="D89" s="0"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0"/>
-      <c r="B90" s="0"/>
-      <c r="C90" s="0"/>
-      <c r="D90" s="0"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0"/>
-      <c r="B91" s="0"/>
-      <c r="C91" s="0"/>
-      <c r="D91" s="0"/>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0"/>
-      <c r="B92" s="0"/>
-      <c r="C92" s="0"/>
-      <c r="D92" s="0"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0"/>
-      <c r="B93" s="0"/>
-      <c r="C93" s="0"/>
-      <c r="D93" s="0"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0"/>
-      <c r="B94" s="0"/>
-      <c r="C94" s="0"/>
-      <c r="D94" s="0"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0"/>
-      <c r="B95" s="0"/>
-      <c r="C95" s="0"/>
-      <c r="D95" s="0"/>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0"/>
-      <c r="B96" s="0"/>
-      <c r="C96" s="0"/>
-      <c r="D96" s="0"/>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0"/>
-      <c r="B97" s="0"/>
-      <c r="C97" s="0"/>
-      <c r="D97" s="0"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0"/>
-      <c r="B98" s="0"/>
-      <c r="C98" s="0"/>
-      <c r="D98" s="0"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0"/>
-      <c r="B99" s="0"/>
-      <c r="C99" s="0"/>
-      <c r="D99" s="0"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0"/>
-      <c r="B100" s="0"/>
-      <c r="C100" s="0"/>
-      <c r="D100" s="0"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0"/>
-      <c r="B101" s="0"/>
-      <c r="C101" s="0"/>
-      <c r="D101" s="0"/>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0"/>
-      <c r="B102" s="0"/>
-      <c r="C102" s="0"/>
-      <c r="D102" s="0"/>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0"/>
-      <c r="B103" s="0"/>
-      <c r="C103" s="0"/>
-      <c r="D103" s="0"/>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0"/>
-      <c r="B104" s="0"/>
-      <c r="C104" s="0"/>
-      <c r="D104" s="0"/>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0"/>
-      <c r="B105" s="0"/>
-      <c r="C105" s="0"/>
-      <c r="D105" s="0"/>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0"/>
-      <c r="B106" s="0"/>
-      <c r="C106" s="0"/>
-      <c r="D106" s="0"/>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0"/>
-      <c r="B107" s="0"/>
-      <c r="C107" s="0"/>
-      <c r="D107" s="0"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0"/>
-      <c r="B108" s="0"/>
-      <c r="C108" s="0"/>
-      <c r="D108" s="0"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0"/>
-      <c r="B109" s="0"/>
-      <c r="C109" s="0"/>
-      <c r="D109" s="0"/>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0"/>
-      <c r="B110" s="0"/>
-      <c r="C110" s="0"/>
-      <c r="D110" s="0"/>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0"/>
-      <c r="B111" s="0"/>
-      <c r="C111" s="0"/>
-      <c r="D111" s="0"/>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0"/>
-      <c r="B112" s="0"/>
-      <c r="C112" s="0"/>
-      <c r="D112" s="0"/>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0"/>
-      <c r="B113" s="0"/>
-      <c r="C113" s="0"/>
-      <c r="D113" s="0"/>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0"/>
-      <c r="B114" s="0"/>
-      <c r="C114" s="0"/>
-      <c r="D114" s="0"/>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0"/>
-      <c r="B115" s="0"/>
-      <c r="C115" s="0"/>
-      <c r="D115" s="0"/>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0"/>
-      <c r="B116" s="0"/>
-      <c r="C116" s="0"/>
-      <c r="D116" s="0"/>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0"/>
-      <c r="B117" s="0"/>
-      <c r="C117" s="0"/>
-      <c r="D117" s="0"/>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0"/>
-      <c r="B118" s="0"/>
-      <c r="C118" s="0"/>
-      <c r="D118" s="0"/>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0"/>
-      <c r="B119" s="0"/>
-      <c r="C119" s="0"/>
-      <c r="D119" s="0"/>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0"/>
-      <c r="B120" s="0"/>
-      <c r="C120" s="0"/>
-      <c r="D120" s="0"/>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0"/>
-      <c r="B121" s="0"/>
-      <c r="C121" s="0"/>
-      <c r="D121" s="0"/>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0"/>
-      <c r="B122" s="0"/>
-      <c r="C122" s="0"/>
-      <c r="D122" s="0"/>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0"/>
-      <c r="B123" s="0"/>
-      <c r="C123" s="0"/>
-      <c r="D123" s="0"/>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0"/>
-      <c r="B124" s="0"/>
-      <c r="C124" s="0"/>
-      <c r="D124" s="0"/>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0"/>
-      <c r="B125" s="0"/>
-      <c r="C125" s="0"/>
-      <c r="D125" s="0"/>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0"/>
-      <c r="B126" s="0"/>
-      <c r="C126" s="0"/>
-      <c r="D126" s="0"/>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0"/>
-      <c r="B127" s="0"/>
-      <c r="C127" s="0"/>
-      <c r="D127" s="0"/>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0"/>
-      <c r="B128" s="0"/>
-      <c r="C128" s="0"/>
-      <c r="D128" s="0"/>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0"/>
-      <c r="B129" s="0"/>
-      <c r="C129" s="0"/>
-      <c r="D129" s="0"/>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0"/>
-      <c r="B130" s="0"/>
-      <c r="C130" s="0"/>
-      <c r="D130" s="0"/>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0"/>
-      <c r="B131" s="0"/>
-      <c r="C131" s="0"/>
-      <c r="D131" s="0"/>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0"/>
-      <c r="B132" s="0"/>
-      <c r="C132" s="0"/>
-      <c r="D132" s="0"/>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0"/>
-      <c r="B133" s="0"/>
-      <c r="C133" s="0"/>
-      <c r="D133" s="0"/>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0"/>
-      <c r="B134" s="0"/>
-      <c r="C134" s="0"/>
-      <c r="D134" s="0"/>
-    </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0"/>
-      <c r="B135" s="0"/>
-      <c r="C135" s="0"/>
-      <c r="D135" s="0"/>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0"/>
-      <c r="B136" s="0"/>
-      <c r="C136" s="0"/>
-      <c r="D136" s="0"/>
-    </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0"/>
-      <c r="B137" s="0"/>
-      <c r="C137" s="0"/>
-      <c r="D137" s="0"/>
-    </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0"/>
-      <c r="B138" s="0"/>
-      <c r="C138" s="0"/>
-      <c r="D138" s="0"/>
-    </row>
-    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0"/>
-      <c r="B139" s="0"/>
-      <c r="C139" s="0"/>
-      <c r="D139" s="0"/>
-    </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0"/>
-      <c r="B140" s="0"/>
-      <c r="C140" s="0"/>
-      <c r="D140" s="0"/>
-    </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0"/>
-      <c r="B141" s="0"/>
-      <c r="C141" s="0"/>
-      <c r="D141" s="0"/>
-    </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0"/>
-      <c r="B142" s="0"/>
-      <c r="C142" s="0"/>
-      <c r="D142" s="0"/>
-    </row>
-    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0"/>
-      <c r="B143" s="0"/>
-      <c r="C143" s="0"/>
-      <c r="D143" s="0"/>
-    </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0"/>
-      <c r="B144" s="0"/>
-      <c r="C144" s="0"/>
-      <c r="D144" s="0"/>
-    </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0"/>
-      <c r="B145" s="0"/>
-      <c r="C145" s="0"/>
-      <c r="D145" s="0"/>
-    </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0"/>
-      <c r="B146" s="0"/>
-      <c r="C146" s="0"/>
-      <c r="D146" s="0"/>
-    </row>
-    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0"/>
-      <c r="B147" s="0"/>
-      <c r="C147" s="0"/>
-      <c r="D147" s="0"/>
-    </row>
-    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0"/>
-      <c r="B148" s="0"/>
-      <c r="C148" s="0"/>
-      <c r="D148" s="0"/>
-    </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0"/>
-      <c r="B149" s="0"/>
-      <c r="C149" s="0"/>
-      <c r="D149" s="0"/>
-    </row>
-    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0"/>
-      <c r="B150" s="0"/>
-      <c r="C150" s="0"/>
-      <c r="D150" s="0"/>
-    </row>
-    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0"/>
-      <c r="B151" s="0"/>
-      <c r="C151" s="0"/>
-      <c r="D151" s="0"/>
-    </row>
-    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0"/>
-      <c r="B152" s="0"/>
-      <c r="C152" s="0"/>
-      <c r="D152" s="0"/>
-    </row>
-    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0"/>
-      <c r="B153" s="0"/>
-      <c r="C153" s="0"/>
-      <c r="D153" s="0"/>
-    </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0"/>
-      <c r="B154" s="0"/>
-      <c r="C154" s="0"/>
-      <c r="D154" s="0"/>
-    </row>
-    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0"/>
-      <c r="B155" s="0"/>
-      <c r="C155" s="0"/>
-      <c r="D155" s="0"/>
-    </row>
-    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0"/>
-      <c r="B156" s="0"/>
-      <c r="C156" s="0"/>
-      <c r="D156" s="0"/>
-    </row>
-    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0"/>
-      <c r="B157" s="0"/>
-      <c r="C157" s="0"/>
-      <c r="D157" s="0"/>
-    </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0"/>
-      <c r="B158" s="0"/>
-      <c r="C158" s="0"/>
-      <c r="D158" s="0"/>
-    </row>
-    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0"/>
-      <c r="B159" s="0"/>
-      <c r="C159" s="0"/>
-      <c r="D159" s="0"/>
-    </row>
-    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0"/>
-      <c r="B160" s="0"/>
-      <c r="C160" s="0"/>
-      <c r="D160" s="0"/>
-    </row>
-    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0"/>
-      <c r="B161" s="0"/>
-      <c r="C161" s="0"/>
-      <c r="D161" s="0"/>
-    </row>
-    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0"/>
-      <c r="B162" s="0"/>
-      <c r="C162" s="0"/>
-      <c r="D162" s="0"/>
-    </row>
-    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0"/>
-      <c r="B163" s="0"/>
-      <c r="C163" s="0"/>
-      <c r="D163" s="0"/>
-    </row>
-    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0"/>
-      <c r="B164" s="0"/>
-      <c r="C164" s="0"/>
-      <c r="D164" s="0"/>
-    </row>
-    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0"/>
-      <c r="B165" s="0"/>
-      <c r="C165" s="0"/>
-      <c r="D165" s="0"/>
-    </row>
-    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0"/>
-      <c r="B166" s="0"/>
-      <c r="C166" s="0"/>
-      <c r="D166" s="0"/>
-    </row>
-    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0"/>
-      <c r="B167" s="0"/>
-      <c r="C167" s="0"/>
-      <c r="D167" s="0"/>
-    </row>
-    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0"/>
-      <c r="B168" s="0"/>
-      <c r="C168" s="0"/>
-      <c r="D168" s="0"/>
-    </row>
-    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0"/>
-      <c r="B169" s="0"/>
-      <c r="C169" s="0"/>
-      <c r="D169" s="0"/>
-    </row>
-    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0"/>
-      <c r="B170" s="0"/>
-      <c r="C170" s="0"/>
-      <c r="D170" s="0"/>
-    </row>
-    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0"/>
-      <c r="B171" s="0"/>
-      <c r="C171" s="0"/>
-      <c r="D171" s="0"/>
-    </row>
-    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0"/>
-      <c r="B172" s="0"/>
-      <c r="C172" s="0"/>
-      <c r="D172" s="0"/>
-    </row>
-    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0"/>
-      <c r="B173" s="0"/>
-      <c r="C173" s="0"/>
-      <c r="D173" s="0"/>
-    </row>
-    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0"/>
-      <c r="B174" s="0"/>
-      <c r="C174" s="0"/>
-      <c r="D174" s="0"/>
-    </row>
-    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0"/>
-      <c r="B175" s="0"/>
-      <c r="C175" s="0"/>
-      <c r="D175" s="0"/>
-    </row>
-    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0"/>
-      <c r="B176" s="0"/>
-      <c r="C176" s="0"/>
-      <c r="D176" s="0"/>
-    </row>
-    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0"/>
-      <c r="B177" s="0"/>
-      <c r="C177" s="0"/>
-      <c r="D177" s="0"/>
-    </row>
-    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0"/>
-      <c r="B178" s="0"/>
-      <c r="C178" s="0"/>
-      <c r="D178" s="0"/>
-    </row>
-    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0"/>
-      <c r="B179" s="0"/>
-      <c r="C179" s="0"/>
-      <c r="D179" s="0"/>
-    </row>
-    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0"/>
-      <c r="B180" s="0"/>
-      <c r="C180" s="0"/>
-      <c r="D180" s="0"/>
-    </row>
-    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0"/>
-      <c r="B181" s="0"/>
-      <c r="C181" s="0"/>
-      <c r="D181" s="0"/>
-    </row>
-    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0"/>
-      <c r="B182" s="0"/>
-      <c r="C182" s="0"/>
-      <c r="D182" s="0"/>
-    </row>
-    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0"/>
-      <c r="B183" s="0"/>
-      <c r="C183" s="0"/>
-      <c r="D183" s="0"/>
-    </row>
-    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0"/>
-      <c r="B184" s="0"/>
-      <c r="C184" s="0"/>
-      <c r="D184" s="0"/>
-    </row>
-    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0"/>
-      <c r="B185" s="0"/>
-      <c r="C185" s="0"/>
-      <c r="D185" s="0"/>
-    </row>
-    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0"/>
-      <c r="B186" s="0"/>
-      <c r="C186" s="0"/>
-      <c r="D186" s="0"/>
-    </row>
-    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0"/>
-      <c r="B187" s="0"/>
-      <c r="C187" s="0"/>
-      <c r="D187" s="0"/>
-    </row>
-    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0"/>
-      <c r="B188" s="0"/>
-      <c r="C188" s="0"/>
-      <c r="D188" s="0"/>
-    </row>
-    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0"/>
-      <c r="B189" s="0"/>
-      <c r="C189" s="0"/>
-      <c r="D189" s="0"/>
-    </row>
-    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0"/>
-      <c r="B190" s="0"/>
-      <c r="C190" s="0"/>
-      <c r="D190" s="0"/>
-    </row>
-    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0"/>
-      <c r="B191" s="0"/>
-      <c r="C191" s="0"/>
-      <c r="D191" s="0"/>
-    </row>
-    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0"/>
-      <c r="B192" s="0"/>
-      <c r="C192" s="0"/>
-      <c r="D192" s="0"/>
-    </row>
-    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0"/>
-      <c r="B193" s="0"/>
-      <c r="C193" s="0"/>
-      <c r="D193" s="0"/>
-    </row>
-    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0"/>
-      <c r="B194" s="0"/>
-      <c r="C194" s="0"/>
-      <c r="D194" s="0"/>
-    </row>
-    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0"/>
-      <c r="B195" s="0"/>
-      <c r="C195" s="0"/>
-      <c r="D195" s="0"/>
-    </row>
-    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0"/>
-      <c r="B196" s="0"/>
-      <c r="C196" s="0"/>
-      <c r="D196" s="0"/>
-    </row>
-    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0"/>
-      <c r="B197" s="0"/>
-      <c r="C197" s="0"/>
-      <c r="D197" s="0"/>
-    </row>
-    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0"/>
-      <c r="B198" s="0"/>
-      <c r="C198" s="0"/>
-      <c r="D198" s="0"/>
-    </row>
-    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="0"/>
-      <c r="B199" s="0"/>
-      <c r="C199" s="0"/>
-      <c r="D199" s="0"/>
-    </row>
-    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="0"/>
-      <c r="B200" s="0"/>
-      <c r="C200" s="0"/>
-      <c r="D200" s="0"/>
-    </row>
-    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="0"/>
-      <c r="B201" s="0"/>
-      <c r="C201" s="0"/>
-      <c r="D201" s="0"/>
-    </row>
-    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="0"/>
-      <c r="B202" s="0"/>
-      <c r="C202" s="0"/>
-      <c r="D202" s="0"/>
-    </row>
-    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="0"/>
-      <c r="B203" s="0"/>
-      <c r="C203" s="0"/>
-      <c r="D203" s="0"/>
-    </row>
-    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="0"/>
-      <c r="B204" s="0"/>
-      <c r="C204" s="0"/>
-      <c r="D204" s="0"/>
-    </row>
-    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="0"/>
-      <c r="B205" s="0"/>
-      <c r="C205" s="0"/>
-      <c r="D205" s="0"/>
-    </row>
-    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="0"/>
-      <c r="B206" s="0"/>
-      <c r="C206" s="0"/>
-      <c r="D206" s="0"/>
-    </row>
-    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="0"/>
-      <c r="B207" s="0"/>
-      <c r="C207" s="0"/>
-      <c r="D207" s="0"/>
-    </row>
-    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="0"/>
-      <c r="B208" s="0"/>
-      <c r="C208" s="0"/>
-      <c r="D208" s="0"/>
-    </row>
-    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="0"/>
-      <c r="B209" s="0"/>
-      <c r="C209" s="0"/>
-      <c r="D209" s="0"/>
-    </row>
-    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="0"/>
-      <c r="B210" s="0"/>
-      <c r="C210" s="0"/>
-      <c r="D210" s="0"/>
-    </row>
-    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="0"/>
-      <c r="B211" s="0"/>
-      <c r="C211" s="0"/>
-      <c r="D211" s="0"/>
-    </row>
-    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="0"/>
-      <c r="B212" s="0"/>
-      <c r="C212" s="0"/>
-      <c r="D212" s="0"/>
-    </row>
-    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="0"/>
-      <c r="B213" s="0"/>
-      <c r="C213" s="0"/>
-      <c r="D213" s="0"/>
-    </row>
-    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="0"/>
-      <c r="B214" s="0"/>
-      <c r="C214" s="0"/>
-      <c r="D214" s="0"/>
-    </row>
-    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="0"/>
-      <c r="B215" s="0"/>
-      <c r="C215" s="0"/>
-      <c r="D215" s="0"/>
-    </row>
-    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="0"/>
-      <c r="B216" s="0"/>
-      <c r="C216" s="0"/>
-      <c r="D216" s="0"/>
-    </row>
-    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="0"/>
-      <c r="B217" s="0"/>
-      <c r="C217" s="0"/>
-      <c r="D217" s="0"/>
-    </row>
-    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="0"/>
-      <c r="B218" s="0"/>
-      <c r="C218" s="0"/>
-      <c r="D218" s="0"/>
-    </row>
-    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="0"/>
-      <c r="B219" s="0"/>
-      <c r="C219" s="0"/>
-      <c r="D219" s="0"/>
-    </row>
-    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="0"/>
-      <c r="B220" s="0"/>
-      <c r="C220" s="0"/>
-      <c r="D220" s="0"/>
-    </row>
-    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="0"/>
-      <c r="B221" s="0"/>
-      <c r="C221" s="0"/>
-      <c r="D221" s="0"/>
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
